--- a/data_extactor/batch_10_fa/trimmed/batch_0070_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0070_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>اداری و دفتری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورت‌حساب و ثبت اسناد | کارمندان دفاتر مالی، حسابداری و حسابرسی | کارمندان مکاتبات و امور اداری | کارشناسان خدمات پس از فروش و امور مشتریان | متصدیان بایگانی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | مسئولان دفاتر و دستیاران اداری (به‌جز حقوقی، پزشکی و اجرایی)</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان بایگانی و اسناد | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | تولید و فرآوری | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | تولید و فرآوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | توجه انتخابی | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | توجه انتخابی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | متصدیان ورود اطلاعات (داده‌آمایان) | متصدیان بایگانی | کارمندان امور پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی | تکنسین‌ها و کارکنان پیش از چاپ | صحافان و کارگران تکمیلی چاپ | اپراتورهای ماشین‌آلات چاپ</t>
+          <t>تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان بایگانی و اسناد | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | کارگران صحافی و تکمیل چاپ | اپراتورهای ماشین‌های چاپ</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | سخن گفتن | شنیدن فعال | تفکر انتقادی</t>
+          <t>درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | دید نزدیک | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | سرعت ادراک</t>
+          <t>درک کتبی | بینایی نزدیک | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارمندان مکاتبات و امور اداری | متخصصان نشر رومیزی | ویراستاران | تکنسین‌های کتابداری | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | نویسندگان متون فنی | متصدیان تایپ و پردازش متن</t>
+          <t>کارشناسان مکاتبات و پاسخ‌گویی به شکایات | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | ویراستاران | تکنسین‌های کتابداری | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | نویسندگان متون فنی | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | شنیدن فعال | سخن گفتن | نظارت</t>
+          <t>ریاضیات | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | گوش دادن فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ریاضیات | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | آموزش و تدریس | اداری و دفتری</t>
+          <t>زبان انگلیسی | ریاضیات | رایانه و الکترونیک | خدمات مشتری و شخصی | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | درک کتبی | کار با اعداد و محاسبات | درک شفاهی | بیان کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>استدلال ریاضی | درک کتبی | توانایی عددی | درک شفاهی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | متصدیان ورود اطلاعات (داده‌آمایان) | دانشمندان داده | تحلیل‌گران داده‌های مالی و محاسبات کمی | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار | پژوهشگران آمارگیری و پیمایش</t>
+          <t>تحلیل‌گران هوش تجاری | متصدیان ورود اطلاعات و داده‌آمایی | دانشمندان داده | تحلیل‌گران کمّی مالی | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک کتبی | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متصدیان امور دفتری و امور عمومی اداری | مسئولان دفاتر و دستیاران اداری (به‌جز حقوقی، پزشکی و اجرایی) | متصدیان ورود اطلاعات (داده‌آمایان) | متصدیان پذیرش و کارمندان اطلاعات | کارشناسان خدمات پس از فروش و امور مشتریان | متصدیان بایگانی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی</t>
+          <t>متصدیان امور دفتری و امور عمومی اداری | منشی‌ها و دستیاران اداری عمومی | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان پذیرش و اطلاعات | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان بایگانی و اسناد | سرپرستان رده‌اول کارکنان اداری و پشتیبانی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | شنیدن فعال | روش‌های یادگیری | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | گوش دادن فعال | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فرآوری | مکانیک | آموزش و تدریس | زیست‌شناسی | تولید مواد غذایی</t>
+          <t>مدیریت و اداره | تولید و فرآوری | مکانیک | آموزش و پرورش | زیست‌شناسی | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | دید نزدیک | دید دور | استدلال استقرایی | استدلال قیاسی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | بینایی نزدیک | بینایی دور | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | مدیران امور کشاورزی و دامپروری | سرپرستان رده‌اول کارگران فضای سبز، باغبانی و محوطه‌سازی | سرپرستان رده‌اول کارگران تولید و عملیات | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | مدیران کل و مدیران عملیاتی | کارشناسان مدیریت مرتع</t>
+          <t>تکنسین‌های کشاورزی | مدیران امور کشاورزی، دامپروری و شیلات | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده اول کارگران تولید و عملیات | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | مدیران کل و مدیران عملیات | مدیران و کارشناسان مدیریت مراتع</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | حقوق و مقررات دولتی | اداری و دفتری | ایمنی و امنیت عمومی | ریاضیات | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | اداری | ایمنی و امنیت عمومی | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان شفاهی | درک کتبی</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | بازرسان انطباق زیست‌محیطی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | تکنسین‌های علوم صنایع غذایی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | بازرسان، آزمون‌گران، درجه‌بندان، نمونه‌برداران و متصدیان توزین | تحلیل‌گران کنترل کیفیت</t>
+          <t>تکنسین‌های کشاورزی | بازرسان رعایت ضوابط زیست‌محیطی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | تکنسین‌های علوم و صنایع غذایی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان تحلیل کنترل کیفیت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | علوم کاربردی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | علوم | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | مدیریت و امور اداری | زیست‌شناسی | ریاضیات | اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | زیست‌شناسی | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | استدلال قیاسی | حساسیت به مسئله | دید دور | استحکام و قدرت بدنی | ثبات دست و بازو | درک شفاهی</t>
+          <t>بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | بینایی دور | قدرت ایستا | ثبات دست و بازو | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>محیط باز و مواجهه با شرایط جوی | استقلال در تصمیم‌گیری | تعیین اولویت‌ها و اهداف کاری | پیامدهای مهم خطای کاری | کار در محیط مسقف باز</t>
+          <t>آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض تمام شرایط آب و هوایی | پیامد خطا | فضای باز، زیر سقف</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | کارگران مراقبت و نگهداری از حیوانات | دانشمندان و کارشناسان علوم دامی | مدیران امور کشاورزی و دامپروری | کارگران مزارع پرورش دام، طیور و آبزیان | دامپزشکان | تکنسین‌ها و کاردان‌های دامپزشکی</t>
+          <t>تکنسین‌های کشاورزی | مراقبان و نگهداران حیوانات | متخصصان علوم دامی | مدیران امور کشاورزی، دامپروری و شیلات | کارگران پرورش دام، طیور و آبزیان | دامپزشکان | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | انعطاف‌پذیری در دسته‌بندی | چابکی انگشتان | درک شفاهی</t>
+          <t>مهارت دستی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | بازرسان محصولات و فرآورده‌های کشاورزی | کارگران زراعت، نهالستان و گلخانه | تکنسین‌های علوم صنایع غذایی | قطعه‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی | بسته‌بندهای دستی کالا | متصدیان توزین، سنجش و نمونه‌برداری</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | بازرسان محصولات و فرآورده‌های کشاورزی | کارگران زراعت، نهالستان و گلخانه | تکنسین‌های علوم و صنایع غذایی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | کارگران بسته‌بندی دستی | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دقت در کنترل | هماهنگی میان اعضای بدن | دید نزدیک | دید دور | حساسیت به مسئله | چابکی دستی | استحکام و قدرت بدنی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی نزدیک | بینایی دور | حساسیت به مسئله | مهارت دستی | قدرت ایستا</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارگران زراعت، نهالستان و گلخانه | مکانیک‌های ماشین‌آلات صنعتی | رانندگان تراکتور و لیفتراک‌های صنعتی | کارگران خدماتی و جابجایی دستی بار | تعمیرکاران و تکنسین‌های نگهداری ماشین‌آلات | مهندسان ماشین‌آلات سنگین و اپراتورهای تجهیزات عمرانی | سم‌پاشان و کارشناسان کاربرد سموم دفع آفات نباتی</t>
+          <t>کارگران زراعت، نهالستان و گلخانه | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
